--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -15483,7 +15483,7 @@
         <v>14.62316117996352</v>
       </c>
       <c r="G488" t="n">
-        <v>12.32701955972908</v>
+        <v>12.32792738055661</v>
       </c>
       <c r="H488" t="n">
         <v>4.3</v>
@@ -15514,7 +15514,7 @@
         <v>14.62288958728487</v>
       </c>
       <c r="G489" t="n">
-        <v>12.32974497188679</v>
+        <v>12.32746693054715</v>
       </c>
       <c r="H489" t="n">
         <v>4.3</v>
@@ -15826,7 +15826,7 @@
         <v>14.58917633294569</v>
       </c>
       <c r="G499" t="n">
-        <v>12.34996517570435</v>
+        <v>12.35063608572153</v>
       </c>
       <c r="H499" t="n">
         <v>4.2</v>
@@ -15857,7 +15857,7 @@
         <v>14.58449824468805</v>
       </c>
       <c r="G500" t="n">
-        <v>12.34339247794596</v>
+        <v>12.34451632807819</v>
       </c>
       <c r="H500" t="n">
         <v>4.1</v>
@@ -15881,7 +15881,9 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>12.35289654997097</v>
+      </c>
       <c r="H501" t="n">
         <v>4.1</v>
       </c>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -15725,7 +15725,7 @@
         <v>3.975936331171799</v>
       </c>
       <c r="E496" t="n">
-        <v>4.622561083872018</v>
+        <v>4.622357631970736</v>
       </c>
       <c r="F496" t="n">
         <v>14.60369469918941</v>
@@ -15756,7 +15756,7 @@
         <v>3.908014984030607</v>
       </c>
       <c r="E497" t="n">
-        <v>4.630055950655107</v>
+        <v>4.630626409392525</v>
       </c>
       <c r="F497" t="n">
         <v>14.58942218568114</v>
@@ -15787,7 +15787,7 @@
         <v>3.802208139420939</v>
       </c>
       <c r="E498" t="n">
-        <v>4.62995937928025</v>
+        <v>4.631223823183653</v>
       </c>
       <c r="F498" t="n">
         <v>14.58949828168852</v>
@@ -15820,7 +15820,7 @@
         <v>3.901972669574645</v>
       </c>
       <c r="E499" t="n">
-        <v>4.632656940107219</v>
+        <v>4.63319382989431</v>
       </c>
       <c r="F499" t="n">
         <v>14.58917633294569</v>
@@ -15851,7 +15851,7 @@
         <v>4.01096295328305</v>
       </c>
       <c r="E500" t="n">
-        <v>4.634669763174896</v>
+        <v>4.635169667815152</v>
       </c>
       <c r="F500" t="n">
         <v>14.58449824468805</v>
@@ -15879,7 +15879,9 @@
         <v>3.72</v>
       </c>
       <c r="D501" t="inlineStr"/>
-      <c r="E501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>4.635390905036694</v>
+      </c>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="n">
         <v>12.35289654997097</v>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -15878,7 +15878,9 @@
       <c r="C501" t="n">
         <v>3.72</v>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="n">
+        <v>3.945457781514384</v>
+      </c>
       <c r="E501" t="n">
         <v>4.635390905036694</v>
       </c>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -13822,7 +13822,7 @@
         <v>44286</v>
       </c>
       <c r="B436" t="n">
-        <v>9.956181230928129</v>
+        <v>9.957341966954106</v>
       </c>
       <c r="C436" t="n">
         <v>0.03</v>
@@ -13917,7 +13917,7 @@
         <v>44377</v>
       </c>
       <c r="B439" t="n">
-        <v>9.973056944469892</v>
+        <v>9.974601765719235</v>
       </c>
       <c r="C439" t="n">
         <v>0.04</v>
@@ -14012,7 +14012,7 @@
         <v>44469</v>
       </c>
       <c r="B442" t="n">
-        <v>9.981273623611811</v>
+        <v>9.982375994301007</v>
       </c>
       <c r="C442" t="n">
         <v>0.04</v>
@@ -14107,7 +14107,7 @@
         <v>44561</v>
       </c>
       <c r="B445" t="n">
-        <v>9.998285646701525</v>
+        <v>9.998872275016623</v>
       </c>
       <c r="C445" t="n">
         <v>0.06</v>
@@ -14202,7 +14202,7 @@
         <v>44651</v>
       </c>
       <c r="B448" t="n">
-        <v>9.995734408788572</v>
+        <v>9.996325679333669</v>
       </c>
       <c r="C448" t="n">
         <v>0.44</v>
@@ -14297,7 +14297,7 @@
         <v>44742</v>
       </c>
       <c r="B451" t="n">
-        <v>9.997298654739424</v>
+        <v>9.99771951490926</v>
       </c>
       <c r="C451" t="n">
         <v>1.49</v>
@@ -14392,7 +14392,7 @@
         <v>44834</v>
       </c>
       <c r="B454" t="n">
-        <v>10.00449171806472</v>
+        <v>10.00443562768063</v>
       </c>
       <c r="C454" t="n">
         <v>3.13</v>
@@ -14487,7 +14487,7 @@
         <v>44926</v>
       </c>
       <c r="B457" t="n">
-        <v>10.01137040941504</v>
+        <v>10.01111007791986</v>
       </c>
       <c r="C457" t="n">
         <v>4.25</v>
@@ -14582,7 +14582,7 @@
         <v>45016</v>
       </c>
       <c r="B460" t="n">
-        <v>10.01858284611429</v>
+        <v>10.01935488774292</v>
       </c>
       <c r="C460" t="n">
         <v>4.69</v>
@@ -14677,7 +14677,7 @@
         <v>45107</v>
       </c>
       <c r="B463" t="n">
-        <v>10.0248419366623</v>
+        <v>10.02471159446736</v>
       </c>
       <c r="C463" t="n">
         <v>5.16</v>
@@ -14772,7 +14772,7 @@
         <v>45199</v>
       </c>
       <c r="B466" t="n">
-        <v>10.0363119640584</v>
+        <v>10.03577800050723</v>
       </c>
       <c r="C466" t="n">
         <v>5.32</v>
@@ -14867,7 +14867,7 @@
         <v>45291</v>
       </c>
       <c r="B469" t="n">
-        <v>10.04471711308486</v>
+        <v>10.0446941031361</v>
       </c>
       <c r="C469" t="n">
         <v>5.24</v>
@@ -14962,7 +14962,7 @@
         <v>45382</v>
       </c>
       <c r="B472" t="n">
-        <v>10.04681352749951</v>
+        <v>10.04827921593509</v>
       </c>
       <c r="C472" t="n">
         <v>5.24</v>
@@ -15057,7 +15057,7 @@
         <v>45473</v>
       </c>
       <c r="B475" t="n">
-        <v>10.05562941604225</v>
+        <v>10.05706981370125</v>
       </c>
       <c r="C475" t="n">
         <v>5.24</v>
@@ -15152,7 +15152,7 @@
         <v>45565</v>
       </c>
       <c r="B478" t="n">
-        <v>10.06384336919129</v>
+        <v>10.06483059094488</v>
       </c>
       <c r="C478" t="n">
         <v>4.72</v>
@@ -15247,7 +15247,7 @@
         <v>45657</v>
       </c>
       <c r="B481" t="n">
-        <v>10.06843157411963</v>
+        <v>10.07076987653533</v>
       </c>
       <c r="C481" t="n">
         <v>4.27</v>
@@ -15342,7 +15342,7 @@
         <v>45747</v>
       </c>
       <c r="B484" t="n">
-        <v>10.0668050880632</v>
+        <v>10.07112740022202</v>
       </c>
       <c r="C484" t="n">
         <v>4.2</v>
@@ -15437,7 +15437,7 @@
         <v>45838</v>
       </c>
       <c r="B487" t="n">
-        <v>10.07622061967116</v>
+        <v>10.08098762965501</v>
       </c>
       <c r="C487" t="n">
         <v>4.23</v>
@@ -15532,7 +15532,7 @@
         <v>45930</v>
       </c>
       <c r="B490" t="n">
-        <v>10.08692656807376</v>
+        <v>10.09050498310292</v>
       </c>
       <c r="C490" t="n">
         <v>3.92</v>
@@ -15621,7 +15621,7 @@
         <v>46022</v>
       </c>
       <c r="B493" t="n">
-        <v>10.08812929062657</v>
+        <v>10.09102378093236</v>
       </c>
       <c r="C493" t="n">
         <v>3.59</v>
@@ -15716,7 +15716,7 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>10.0932984523892</v>
+        <v>10.09717687574073</v>
       </c>
       <c r="C496" t="n">
         <v>3.61</v>
@@ -15811,7 +15811,7 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>10.09698035298165</v>
+        <v>10.10266667706832</v>
       </c>
       <c r="C499" t="n">
         <v>3.66</v>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15823,7 +15823,7 @@
         <v>4.63319382989431</v>
       </c>
       <c r="F499" t="n">
-        <v>14.58917633294569</v>
+        <v>14.59820132343421</v>
       </c>
       <c r="G499" t="n">
         <v>12.35063608572153</v>
@@ -15854,7 +15854,7 @@
         <v>4.635169667815152</v>
       </c>
       <c r="F500" t="n">
-        <v>14.58449824468805</v>
+        <v>14.59688562526572</v>
       </c>
       <c r="G500" t="n">
         <v>12.34451632807819</v>
@@ -15884,7 +15884,9 @@
       <c r="E501" t="n">
         <v>4.635390905036694</v>
       </c>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="n">
+        <v>14.60538918058396</v>
+      </c>
       <c r="G501" t="n">
         <v>12.35289654997097</v>
       </c>
@@ -15898,6 +15900,23 @@
         <v>4.511738241195538</v>
       </c>
       <c r="K501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -15913,7 +15913,9 @@
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
+      <c r="H502" t="n">
+        <v>4.2</v>
+      </c>
       <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -15917,7 +15917,9 @@
         <v>4.2</v>
       </c>
       <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>4.737600973168581</v>
+      </c>
       <c r="K502" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,64 +421,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDPlevel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TBILL3M</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ConsSent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CONSspend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CPI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>BrentUSD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>SP500</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -517,7 +503,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -542,7 +528,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="n">
@@ -569,7 +555,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -594,7 +580,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -619,7 +605,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="n">
@@ -646,7 +632,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -671,7 +657,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -696,7 +682,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="n">
@@ -723,7 +709,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -748,7 +734,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -773,7 +759,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="n">
@@ -800,7 +786,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -825,7 +811,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -850,7 +836,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="n">
@@ -877,7 +863,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -902,7 +888,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -927,7 +913,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="n">
@@ -954,7 +940,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -979,7 +965,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1004,7 +990,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="n">
@@ -1031,7 +1017,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1056,7 +1042,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1081,7 +1067,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="n">
@@ -1108,7 +1094,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1133,7 +1119,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1158,7 +1144,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="n">
@@ -1185,7 +1171,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1210,7 +1196,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1237,7 +1223,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="n">
@@ -1266,7 +1252,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1293,7 +1279,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1320,7 +1306,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="n">
@@ -1349,7 +1335,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1376,7 +1362,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1403,7 +1389,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="n">
@@ -1432,7 +1418,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1459,7 +1445,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1486,7 +1472,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="n">
@@ -1515,7 +1501,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1542,7 +1528,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1569,7 +1555,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="n">
@@ -1598,7 +1584,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1625,7 +1611,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1652,7 +1638,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="n">
@@ -1681,7 +1667,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1708,7 +1694,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1735,7 +1721,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="n">
@@ -1764,7 +1750,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1791,7 +1777,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1818,7 +1804,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="n">
@@ -1847,7 +1833,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1874,7 +1860,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1901,7 +1887,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="n">
@@ -1930,7 +1916,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1957,7 +1943,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1984,7 +1970,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="n">
@@ -2013,7 +1999,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2040,7 +2026,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2067,7 +2053,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="n">
@@ -2096,7 +2082,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2123,7 +2109,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2150,7 +2136,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="n">
@@ -2179,7 +2165,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2206,7 +2192,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2233,7 +2219,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="n">
@@ -2262,7 +2248,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2289,7 +2275,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2316,7 +2302,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="n">
@@ -2345,7 +2331,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2372,7 +2358,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2399,7 +2385,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="n">
@@ -2428,7 +2414,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2455,7 +2441,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2482,7 +2468,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="n">
@@ -2511,7 +2497,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2538,7 +2524,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2565,7 +2551,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="n">
@@ -2594,7 +2580,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2621,7 +2607,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2648,7 +2634,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="n">
@@ -2677,7 +2663,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2704,7 +2690,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2731,7 +2717,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="n">
@@ -2760,7 +2746,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2789,7 +2775,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2818,7 +2804,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="n">
@@ -2849,7 +2835,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2878,7 +2864,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2907,7 +2893,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="n">
@@ -2938,7 +2924,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2967,7 +2953,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2996,7 +2982,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="n">
@@ -3027,7 +3013,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3056,7 +3042,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3085,7 +3071,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="n">
@@ -3116,7 +3102,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3147,7 +3133,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3178,7 +3164,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="n">
@@ -3211,7 +3197,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3242,7 +3228,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3273,7 +3259,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="n">
@@ -3306,7 +3292,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -3337,7 +3323,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -3368,7 +3354,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="n">
@@ -3401,7 +3387,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -3432,7 +3418,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3463,7 +3449,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="n">
@@ -3496,7 +3482,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -3527,7 +3513,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3558,7 +3544,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="n">
@@ -3591,7 +3577,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -3622,7 +3608,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3653,7 +3639,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="n">
@@ -3686,7 +3672,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -3717,7 +3703,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3748,7 +3734,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="n">
@@ -3781,7 +3767,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3812,7 +3798,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3843,7 +3829,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="n">
@@ -3876,7 +3862,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -3907,7 +3893,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -3938,7 +3924,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -3971,7 +3957,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4002,7 +3988,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4033,7 +4019,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -4066,7 +4052,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4097,7 +4083,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4128,7 +4114,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -4161,7 +4147,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4192,7 +4178,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4223,7 +4209,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -4256,7 +4242,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -4287,7 +4273,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4318,7 +4304,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -4351,7 +4337,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -4382,7 +4368,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4413,7 +4399,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -4446,7 +4432,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -4477,7 +4463,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -4508,7 +4494,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -4541,7 +4527,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -4572,7 +4558,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -4603,7 +4589,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -4636,7 +4622,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -4667,7 +4653,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4698,7 +4684,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -4731,7 +4717,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -4762,7 +4748,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4793,7 +4779,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -4826,7 +4812,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -4857,7 +4843,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -4888,7 +4874,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -4921,7 +4907,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -4952,7 +4938,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -4983,7 +4969,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -5016,7 +5002,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -5047,7 +5033,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5078,7 +5064,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -5111,7 +5097,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5142,7 +5128,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5173,7 +5159,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -5206,7 +5192,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -5237,7 +5223,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5268,7 +5254,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -5301,7 +5287,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -5332,7 +5318,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -5363,7 +5349,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -5396,7 +5382,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -5427,7 +5413,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -5458,7 +5444,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -5491,7 +5477,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5522,7 +5508,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5553,7 +5539,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -5586,7 +5572,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -5617,7 +5603,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -5648,7 +5634,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -5681,7 +5667,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -5712,7 +5698,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -5743,7 +5729,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -5776,7 +5762,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -5807,7 +5793,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -5838,7 +5824,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -5871,7 +5857,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -5902,7 +5888,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -5933,7 +5919,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -5966,7 +5952,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -5997,7 +5983,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -6028,7 +6014,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -6061,7 +6047,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -6092,7 +6078,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -6123,7 +6109,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -6156,7 +6142,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -6187,7 +6173,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -6218,7 +6204,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -6251,7 +6237,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -6282,7 +6268,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -6313,7 +6299,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -6346,7 +6332,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -6377,7 +6363,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -6408,7 +6394,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -6441,7 +6427,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -6472,7 +6458,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -6503,7 +6489,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -6536,7 +6522,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -6567,7 +6553,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -6598,7 +6584,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -6631,7 +6617,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -6662,7 +6648,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -6693,7 +6679,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -6726,7 +6712,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -6757,7 +6743,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -6788,7 +6774,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -6821,7 +6807,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -6852,7 +6838,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -6883,7 +6869,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -6916,7 +6902,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -6947,7 +6933,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -6978,7 +6964,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -7011,7 +6997,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -7042,7 +7028,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -7073,7 +7059,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -7106,7 +7092,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -7137,7 +7123,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -7168,7 +7154,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -7201,7 +7187,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -7232,7 +7218,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -7263,7 +7249,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -7296,7 +7282,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -7327,7 +7313,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -7358,7 +7344,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -7391,7 +7377,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -7422,7 +7408,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -7453,7 +7439,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -7486,7 +7472,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -7517,7 +7503,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -7548,7 +7534,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -7581,7 +7567,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -7612,7 +7598,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -7643,7 +7629,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -7676,7 +7662,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -7707,7 +7693,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -7738,7 +7724,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -7771,7 +7757,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -7802,7 +7788,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -7833,7 +7819,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -7866,7 +7852,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -7897,7 +7883,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -7928,7 +7914,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -7961,7 +7947,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7992,7 +7978,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -8023,7 +8009,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -8056,7 +8042,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -8087,7 +8073,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -8118,7 +8104,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -8151,7 +8137,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -8182,7 +8168,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -8213,7 +8199,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -8246,7 +8232,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -8277,7 +8263,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -8308,7 +8294,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -8341,7 +8327,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -8372,7 +8358,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -8403,7 +8389,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -8436,7 +8422,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -8467,7 +8453,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -8498,7 +8484,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -8531,7 +8517,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -8562,7 +8548,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -8593,7 +8579,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -8626,7 +8612,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -8657,7 +8643,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -8688,7 +8674,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -8721,7 +8707,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -8752,7 +8738,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -8783,7 +8769,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -8816,7 +8802,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -8847,7 +8833,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -8878,7 +8864,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -8911,7 +8897,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -8942,7 +8928,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -8973,7 +8959,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -9006,7 +8992,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -9037,7 +9023,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -9068,7 +9054,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -9101,7 +9087,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -9132,7 +9118,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -9163,7 +9149,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -9196,7 +9182,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -9227,7 +9213,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -9258,7 +9244,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -9291,7 +9277,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -9322,7 +9308,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -9353,7 +9339,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -9386,7 +9372,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -9417,7 +9403,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -9448,7 +9434,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -9481,7 +9467,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -9512,7 +9498,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -9543,7 +9529,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -9576,7 +9562,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -9607,7 +9593,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -9638,7 +9624,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -9671,7 +9657,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -9702,7 +9688,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -9733,7 +9719,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -9766,7 +9752,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -9797,7 +9783,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -9828,7 +9814,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -9861,7 +9847,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -9892,7 +9878,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -9923,7 +9909,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -9956,7 +9942,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -9987,7 +9973,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -10018,7 +10004,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -10051,7 +10037,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -10082,7 +10068,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -10113,7 +10099,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -10146,7 +10132,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -10177,7 +10163,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -10208,7 +10194,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -10241,7 +10227,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -10272,7 +10258,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -10303,7 +10289,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -10336,7 +10322,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -10367,7 +10353,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -10398,7 +10384,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -10431,7 +10417,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -10462,7 +10448,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -10493,7 +10479,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -10526,7 +10512,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -10557,7 +10543,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -10588,7 +10574,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -10621,7 +10607,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -10652,7 +10638,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -10683,7 +10669,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -10716,7 +10702,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -10747,7 +10733,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -10778,7 +10764,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -10811,7 +10797,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -10842,7 +10828,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -10873,7 +10859,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -10906,7 +10892,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -10937,7 +10923,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -10968,7 +10954,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -11001,7 +10987,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -11032,7 +11018,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -11063,7 +11049,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -11096,7 +11082,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -11127,7 +11113,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -11158,7 +11144,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -11191,7 +11177,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -11222,7 +11208,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -11253,7 +11239,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -11286,7 +11272,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -11317,7 +11303,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -11348,7 +11334,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -11381,7 +11367,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -11412,7 +11398,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -11443,7 +11429,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -11476,7 +11462,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -11493,7 +11479,7 @@
         <v>13.87494953600636</v>
       </c>
       <c r="G362" t="n">
-        <v>12.11402862601247</v>
+        <v>12.11397380385553</v>
       </c>
       <c r="H362" t="n">
         <v>5.7</v>
@@ -11507,7 +11493,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -11524,7 +11510,7 @@
         <v>13.88587116034741</v>
       </c>
       <c r="G363" t="n">
-        <v>12.10895032478981</v>
+        <v>12.10891726438846</v>
       </c>
       <c r="H363" t="n">
         <v>5.5</v>
@@ -11538,7 +11524,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -11557,7 +11543,7 @@
         <v>13.89870030849968</v>
       </c>
       <c r="G364" t="n">
-        <v>12.12142392980245</v>
+        <v>12.12136406960321</v>
       </c>
       <c r="H364" t="n">
         <v>5.4</v>
@@ -11571,7 +11557,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -11588,7 +11574,7 @@
         <v>13.92491996578442</v>
       </c>
       <c r="G365" t="n">
-        <v>12.12227790778691</v>
+        <v>12.12238120598988</v>
       </c>
       <c r="H365" t="n">
         <v>5.4</v>
@@ -11602,7 +11588,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -11619,7 +11605,7 @@
         <v>13.94252463394321</v>
       </c>
       <c r="G366" t="n">
-        <v>12.12676966419164</v>
+        <v>12.12677507683829</v>
       </c>
       <c r="H366" t="n">
         <v>5.6</v>
@@ -11633,7 +11619,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -11652,7 +11638,7 @@
         <v>13.9623715898944</v>
       </c>
       <c r="G367" t="n">
-        <v>12.12420619251028</v>
+        <v>12.12413021786406</v>
       </c>
       <c r="H367" t="n">
         <v>5.3</v>
@@ -11666,7 +11652,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -11683,7 +11669,7 @@
         <v>13.95923074310673</v>
       </c>
       <c r="G368" t="n">
-        <v>12.1316884813928</v>
+        <v>12.13185005142299</v>
       </c>
       <c r="H368" t="n">
         <v>5.2</v>
@@ -11697,7 +11683,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -11714,7 +11700,7 @@
         <v>13.9676967379962</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1314837885391</v>
+        <v>12.13160768658733</v>
       </c>
       <c r="H369" t="n">
         <v>5.1</v>
@@ -11728,7 +11714,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -11747,7 +11733,7 @@
         <v>13.96731878209744</v>
       </c>
       <c r="G370" t="n">
-        <v>12.12924019612577</v>
+        <v>12.12907280364131</v>
       </c>
       <c r="H370" t="n">
         <v>5</v>
@@ -11761,7 +11747,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -11778,7 +11764,7 @@
         <v>13.95660465610406</v>
       </c>
       <c r="G371" t="n">
-        <v>12.12557816915786</v>
+        <v>12.125859923405</v>
       </c>
       <c r="H371" t="n">
         <v>5</v>
@@ -11792,7 +11778,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -11809,7 +11795,7 @@
         <v>13.95136051064989</v>
       </c>
       <c r="G372" t="n">
-        <v>12.12804623709178</v>
+        <v>12.12818137186189</v>
       </c>
       <c r="H372" t="n">
         <v>5.1</v>
@@ -11823,7 +11809,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -11842,7 +11828,7 @@
         <v>13.96078250970982</v>
       </c>
       <c r="G373" t="n">
-        <v>12.13330838557533</v>
+        <v>12.13331914028724</v>
       </c>
       <c r="H373" t="n">
         <v>5</v>
@@ -11856,7 +11842,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -11873,7 +11859,7 @@
         <v>13.9647819247093</v>
       </c>
       <c r="G374" t="n">
-        <v>12.12767857810216</v>
+        <v>12.12719176267673</v>
       </c>
       <c r="H374" t="n">
         <v>4.8</v>
@@ -11887,7 +11873,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -11904,7 +11890,7 @@
         <v>13.97494809484436</v>
       </c>
       <c r="G375" t="n">
-        <v>12.13728511010319</v>
+        <v>12.13748861902615</v>
       </c>
       <c r="H375" t="n">
         <v>4.9</v>
@@ -11918,7 +11904,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -11937,7 +11923,7 @@
         <v>13.98843476431654</v>
       </c>
       <c r="G376" t="n">
-        <v>12.13130060677918</v>
+        <v>12.13120900331435</v>
       </c>
       <c r="H376" t="n">
         <v>5</v>
@@ -11951,7 +11937,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -11968,7 +11954,7 @@
         <v>13.9860142244343</v>
       </c>
       <c r="G377" t="n">
-        <v>12.13289424119438</v>
+        <v>12.13284582351116</v>
       </c>
       <c r="H377" t="n">
         <v>5.1</v>
@@ -11982,7 +11968,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -11999,7 +11985,7 @@
         <v>13.99003932972827</v>
       </c>
       <c r="G378" t="n">
-        <v>12.13330838557533</v>
+        <v>12.13320083209426</v>
       </c>
       <c r="H378" t="n">
         <v>4.8</v>
@@ -12013,7 +11999,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -12032,7 +12018,7 @@
         <v>14.01239555123528</v>
       </c>
       <c r="G379" t="n">
-        <v>12.14113404437126</v>
+        <v>12.14151279083171</v>
       </c>
       <c r="H379" t="n">
         <v>4.9</v>
@@ -12046,7 +12032,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -12063,7 +12049,7 @@
         <v>14.00986937536873</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1406430608467</v>
+        <v>12.14054697064997</v>
       </c>
       <c r="H380" t="n">
         <v>4.8</v>
@@ -12077,7 +12063,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -12094,7 +12080,7 @@
         <v>14.01538548233913</v>
       </c>
       <c r="G381" t="n">
-        <v>12.13914727814006</v>
+        <v>12.13909381592714</v>
       </c>
       <c r="H381" t="n">
         <v>4.9</v>
@@ -12108,7 +12094,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -12127,7 +12113,7 @@
         <v>14.02450487937405</v>
       </c>
       <c r="G382" t="n">
-        <v>12.14341502106357</v>
+        <v>12.14375565496526</v>
       </c>
       <c r="H382" t="n">
         <v>5</v>
@@ -12141,7 +12127,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -12158,7 +12144,7 @@
         <v>14.03150864111761</v>
       </c>
       <c r="G383" t="n">
-        <v>12.14281863239219</v>
+        <v>12.14295711146609</v>
       </c>
       <c r="H383" t="n">
         <v>4.9</v>
@@ -12172,7 +12158,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -12189,7 +12175,7 @@
         <v>14.05048860457254</v>
       </c>
       <c r="G384" t="n">
-        <v>12.1417421027636</v>
+        <v>12.14137411159124</v>
       </c>
       <c r="H384" t="n">
         <v>4.7</v>
@@ -12203,7 +12189,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -12222,7 +12208,7 @@
         <v>14.05487621650924</v>
       </c>
       <c r="G385" t="n">
-        <v>12.1510724892113</v>
+        <v>12.15172733003973</v>
       </c>
       <c r="H385" t="n">
         <v>4.7</v>
@@ -12236,7 +12222,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -12253,7 +12239,7 @@
         <v>14.04346253027079</v>
       </c>
       <c r="G386" t="n">
-        <v>12.15809490125831</v>
+        <v>12.15770139360475</v>
       </c>
       <c r="H386" t="n">
         <v>4.7</v>
@@ -12267,7 +12253,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -12284,7 +12270,7 @@
         <v>14.06028017114614</v>
       </c>
       <c r="G387" t="n">
-        <v>12.15623092867296</v>
+        <v>12.15628348252753</v>
       </c>
       <c r="H387" t="n">
         <v>4.6</v>
@@ -12298,7 +12284,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -12317,7 +12303,7 @@
         <v>14.05803782531418</v>
       </c>
       <c r="G388" t="n">
-        <v>12.15537917121459</v>
+        <v>12.15520031515642</v>
       </c>
       <c r="H388" t="n">
         <v>4.4</v>
@@ -12331,7 +12317,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -12348,7 +12334,7 @@
         <v>14.05313199704229</v>
       </c>
       <c r="G389" t="n">
-        <v>12.15759643207306</v>
+        <v>12.15756494146513</v>
       </c>
       <c r="H389" t="n">
         <v>4.4</v>
@@ -12362,7 +12348,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -12379,7 +12365,7 @@
         <v>14.06402473586785</v>
       </c>
       <c r="G390" t="n">
-        <v>12.15293554711704</v>
+        <v>12.1529460928036</v>
       </c>
       <c r="H390" t="n">
         <v>4.4</v>
@@ -12393,7 +12379,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -12412,7 +12398,7 @@
         <v>14.06037019885516</v>
       </c>
       <c r="G391" t="n">
-        <v>12.15740747354889</v>
+        <v>12.15764366612567</v>
       </c>
       <c r="H391" t="n">
         <v>4.3</v>
@@ -12426,7 +12412,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -12443,7 +12429,7 @@
         <v>14.05894289289133</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1569926893751</v>
+        <v>12.15713447040766</v>
       </c>
       <c r="H392" t="n">
         <v>4.3</v>
@@ -12457,7 +12443,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -12474,7 +12460,7 @@
         <v>14.05770586650698</v>
       </c>
       <c r="G393" t="n">
-        <v>12.15514770434488</v>
+        <v>12.15512665924523</v>
       </c>
       <c r="H393" t="n">
         <v>4.4</v>
@@ -12488,7 +12474,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -12507,7 +12493,7 @@
         <v>14.0623909481895</v>
       </c>
       <c r="G394" t="n">
-        <v>12.17066306079228</v>
+        <v>12.17052836600528</v>
       </c>
       <c r="H394" t="n">
         <v>4.3</v>
@@ -12521,7 +12507,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -12538,7 +12524,7 @@
         <v>14.06540508978025</v>
       </c>
       <c r="G395" t="n">
-        <v>12.17069414162836</v>
+        <v>12.17035219928894</v>
       </c>
       <c r="H395" t="n">
         <v>4.2</v>
@@ -12552,7 +12538,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -12569,7 +12555,7 @@
         <v>14.08500320121584</v>
       </c>
       <c r="G396" t="n">
-        <v>12.17815145167577</v>
+        <v>12.17851129704896</v>
       </c>
       <c r="H396" t="n">
         <v>4.2</v>
@@ -12583,7 +12569,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -12602,7 +12588,7 @@
         <v>14.08885660896575</v>
       </c>
       <c r="G397" t="n">
-        <v>12.18151352402947</v>
+        <v>12.18149302655578</v>
       </c>
       <c r="H397" t="n">
         <v>4.1</v>
@@ -12616,7 +12602,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -12633,7 +12619,7 @@
         <v>14.10703772854232</v>
       </c>
       <c r="G398" t="n">
-        <v>12.17276402148643</v>
+        <v>12.17229867192296</v>
       </c>
       <c r="H398" t="n">
         <v>4</v>
@@ -12647,7 +12633,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -12664,7 +12650,7 @@
         <v>14.11913339855948</v>
       </c>
       <c r="G399" t="n">
-        <v>12.17550002955311</v>
+        <v>12.17589690302011</v>
       </c>
       <c r="H399" t="n">
         <v>4.1</v>
@@ -12678,7 +12664,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -12697,7 +12683,7 @@
         <v>14.11244717471143</v>
       </c>
       <c r="G400" t="n">
-        <v>12.175469097732</v>
+        <v>12.17616483239141</v>
       </c>
       <c r="H400" t="n">
         <v>4</v>
@@ -12711,7 +12697,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -12728,7 +12714,7 @@
         <v>14.11820217155823</v>
       </c>
       <c r="G401" t="n">
-        <v>12.17296043741329</v>
+        <v>12.17316198207291</v>
       </c>
       <c r="H401" t="n">
         <v>4</v>
@@ -12742,7 +12728,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -12759,7 +12745,7 @@
         <v>14.12352673410069</v>
       </c>
       <c r="G402" t="n">
-        <v>12.18670122525088</v>
+        <v>12.18719049446574</v>
       </c>
       <c r="H402" t="n">
         <v>3.8</v>
@@ -12773,7 +12759,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -12792,7 +12778,7 @@
         <v>14.10971928539153</v>
       </c>
       <c r="G403" t="n">
-        <v>12.18227163534422</v>
+        <v>12.18276307609455</v>
       </c>
       <c r="H403" t="n">
         <v>4</v>
@@ -12806,7 +12792,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -12823,7 +12809,7 @@
         <v>14.10445982718298</v>
       </c>
       <c r="G404" t="n">
-        <v>12.18741975703096</v>
+        <v>12.18790358323985</v>
       </c>
       <c r="H404" t="n">
         <v>3.8</v>
@@ -12837,7 +12823,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -12854,7 +12840,7 @@
         <v>14.10753892159392</v>
       </c>
       <c r="G405" t="n">
-        <v>12.18624741797861</v>
+        <v>12.18687963238153</v>
       </c>
       <c r="H405" t="n">
         <v>3.8</v>
@@ -12868,7 +12854,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -12887,7 +12873,7 @@
         <v>14.09559761113762</v>
       </c>
       <c r="G406" t="n">
-        <v>12.18025214711565</v>
+        <v>12.18073432451498</v>
       </c>
       <c r="H406" t="n">
         <v>3.7</v>
@@ -12901,7 +12887,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -12918,7 +12904,7 @@
         <v>14.09005495788187</v>
       </c>
       <c r="G407" t="n">
-        <v>12.18785266518735</v>
+        <v>12.18815813461987</v>
       </c>
       <c r="H407" t="n">
         <v>3.8</v>
@@ -12932,7 +12918,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -12949,7 +12935,7 @@
         <v>14.07996571192112</v>
       </c>
       <c r="G408" t="n">
-        <v>12.1934533561738</v>
+        <v>12.19465268530058</v>
       </c>
       <c r="H408" t="n">
         <v>3.8</v>
@@ -12963,7 +12949,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -12982,7 +12968,7 @@
         <v>14.07173679243951</v>
       </c>
       <c r="G409" t="n">
-        <v>12.17305346307294</v>
+        <v>12.17461293771188</v>
       </c>
       <c r="H409" t="n">
         <v>3.9</v>
@@ -12996,7 +12982,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -13013,7 +12999,7 @@
         <v>14.07437408661561</v>
       </c>
       <c r="G410" t="n">
-        <v>12.17657689130106</v>
+        <v>12.17728729409842</v>
       </c>
       <c r="H410" t="n">
         <v>4</v>
@@ -13027,7 +13013,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -13044,7 +13030,7 @@
         <v>14.0855865489458</v>
       </c>
       <c r="G411" t="n">
-        <v>12.17624725775786</v>
+        <v>12.17742108162345</v>
       </c>
       <c r="H411" t="n">
         <v>3.8</v>
@@ -13058,7 +13044,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -13077,7 +13063,7 @@
         <v>14.09274069878225</v>
       </c>
       <c r="G412" t="n">
-        <v>12.18769480274631</v>
+        <v>12.18833628203988</v>
       </c>
       <c r="H412" t="n">
         <v>3.8</v>
@@ -13091,7 +13077,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -13108,7 +13094,7 @@
         <v>14.11774177643058</v>
       </c>
       <c r="G413" t="n">
-        <v>12.18404173745935</v>
+        <v>12.18457317941694</v>
       </c>
       <c r="H413" t="n">
         <v>3.7</v>
@@ -13122,7 +13108,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -13139,7 +13125,7 @@
         <v>14.12636091107089</v>
       </c>
       <c r="G414" t="n">
-        <v>12.19454647369155</v>
+        <v>12.19576470074076</v>
       </c>
       <c r="H414" t="n">
         <v>3.6</v>
@@ -13153,7 +13139,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -13172,7 +13158,7 @@
         <v>14.13859138572281</v>
       </c>
       <c r="G415" t="n">
-        <v>12.19588088553534</v>
+        <v>12.19673417745079</v>
       </c>
       <c r="H415" t="n">
         <v>3.6</v>
@@ -13186,7 +13172,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -13203,7 +13189,7 @@
         <v>14.16124123125529</v>
       </c>
       <c r="G416" t="n">
-        <v>12.20115055187738</v>
+        <v>12.20173324393108</v>
       </c>
       <c r="H416" t="n">
         <v>3.7</v>
@@ -13217,7 +13203,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -13234,7 +13220,7 @@
         <v>14.17037406223637</v>
       </c>
       <c r="G417" t="n">
-        <v>12.20702718980779</v>
+        <v>12.20831512928295</v>
       </c>
       <c r="H417" t="n">
         <v>3.6</v>
@@ -13248,7 +13234,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -13267,7 +13253,7 @@
         <v>14.17889663180867</v>
       </c>
       <c r="G418" t="n">
-        <v>12.19907320650993</v>
+        <v>12.1995061331004</v>
       </c>
       <c r="H418" t="n">
         <v>3.5</v>
@@ -13281,7 +13267,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -13298,7 +13284,7 @@
         <v>14.18371676064869</v>
       </c>
       <c r="G419" t="n">
-        <v>12.1989271773693</v>
+        <v>12.19942560280838</v>
       </c>
       <c r="H419" t="n">
         <v>3.6</v>
@@ -13312,7 +13298,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -13329,7 +13315,7 @@
         <v>14.1972838858156</v>
       </c>
       <c r="G420" t="n">
-        <v>12.20307816654985</v>
+        <v>12.20392033096203</v>
       </c>
       <c r="H420" t="n">
         <v>3.6</v>
@@ -13343,7 +13329,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -13362,7 +13348,7 @@
         <v>14.20031979486718</v>
       </c>
       <c r="G421" t="n">
-        <v>12.20337400747984</v>
+        <v>12.20416081915422</v>
       </c>
       <c r="H421" t="n">
         <v>3.6</v>
@@ -13376,7 +13362,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -13393,7 +13379,7 @@
         <v>14.21507093407077</v>
       </c>
       <c r="G422" t="n">
-        <v>12.20000427012857</v>
+        <v>12.20058260278654</v>
       </c>
       <c r="H422" t="n">
         <v>3.6</v>
@@ -13407,7 +13393,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -13424,7 +13410,7 @@
         <v>14.21989308028785</v>
       </c>
       <c r="G423" t="n">
-        <v>12.19993887234653</v>
+        <v>12.20085405232875</v>
       </c>
       <c r="H423" t="n">
         <v>3.5</v>
@@ -13438,7 +13424,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -13457,7 +13443,7 @@
         <v>14.22209237565347</v>
       </c>
       <c r="G424" t="n">
-        <v>12.1088290979743</v>
+        <v>12.10949015668385</v>
       </c>
       <c r="H424" t="n">
         <v>4.4</v>
@@ -13471,7 +13457,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -13488,7 +13474,7 @@
         <v>14.19323166940795</v>
       </c>
       <c r="G425" t="n">
-        <v>11.96165438393711</v>
+        <v>11.96446594441912</v>
       </c>
       <c r="H425" t="n">
         <v>14.8</v>
@@ -13502,7 +13488,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -13519,7 +13505,7 @@
         <v>14.18625722911267</v>
       </c>
       <c r="G426" t="n">
-        <v>12.13907243024165</v>
+        <v>12.14283993811331</v>
       </c>
       <c r="H426" t="n">
         <v>13.2</v>
@@ -13533,7 +13519,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -13552,7 +13538,7 @@
         <v>14.19466865103542</v>
       </c>
       <c r="G427" t="n">
-        <v>12.21373322819679</v>
+        <v>12.21558723789876</v>
       </c>
       <c r="H427" t="n">
         <v>11</v>
@@ -13566,7 +13552,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -13583,7 +13569,7 @@
         <v>14.20390681859271</v>
       </c>
       <c r="G428" t="n">
-        <v>12.22448214601292</v>
+        <v>12.22568407807921</v>
       </c>
       <c r="H428" t="n">
         <v>10.2</v>
@@ -13597,7 +13583,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -13614,7 +13600,7 @@
         <v>14.21430479856283</v>
       </c>
       <c r="G429" t="n">
-        <v>12.22913954712434</v>
+        <v>12.22967686115335</v>
       </c>
       <c r="H429" t="n">
         <v>8.4</v>
@@ -13628,7 +13614,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -13647,7 +13633,7 @@
         <v>14.22929760911526</v>
       </c>
       <c r="G430" t="n">
-        <v>12.2462304195048</v>
+        <v>12.24611994004786</v>
       </c>
       <c r="H430" t="n">
         <v>7.8</v>
@@ -13661,7 +13647,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -13678,7 +13664,7 @@
         <v>14.24617676724675</v>
       </c>
       <c r="G431" t="n">
-        <v>12.24094256152308</v>
+        <v>12.24160386856983</v>
       </c>
       <c r="H431" t="n">
         <v>6.9</v>
@@ -13692,7 +13678,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -13709,7 +13695,7 @@
         <v>14.25534939514371</v>
       </c>
       <c r="G432" t="n">
-        <v>12.22903204966508</v>
+        <v>12.2301504350092</v>
       </c>
       <c r="H432" t="n">
         <v>6.7</v>
@@ -13723,7 +13709,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -13742,7 +13728,7 @@
         <v>14.27135504296459</v>
       </c>
       <c r="G433" t="n">
-        <v>12.23328403455772</v>
+        <v>12.23490788509249</v>
       </c>
       <c r="H433" t="n">
         <v>6.7</v>
@@ -13756,7 +13742,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -13773,7 +13759,7 @@
         <v>14.28469948042655</v>
       </c>
       <c r="G434" t="n">
-        <v>12.26852148480266</v>
+        <v>12.26942765409295</v>
       </c>
       <c r="H434" t="n">
         <v>6.4</v>
@@ -13787,7 +13773,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -13804,7 +13790,7 @@
         <v>14.26956072984514</v>
       </c>
       <c r="G435" t="n">
-        <v>12.23915919851796</v>
+        <v>12.24012135304457</v>
       </c>
       <c r="H435" t="n">
         <v>6.2</v>
@@ -13818,7 +13804,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -13851,7 +13837,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -13868,7 +13854,7 @@
         <v>14.29444791238578</v>
       </c>
       <c r="G437" t="n">
-        <v>12.33887564794294</v>
+        <v>12.33934838047706</v>
       </c>
       <c r="H437" t="n">
         <v>6.1</v>
@@ -13882,7 +13868,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -13899,7 +13885,7 @@
         <v>14.30197606885574</v>
       </c>
       <c r="G438" t="n">
-        <v>12.32620403276041</v>
+        <v>12.32671381505009</v>
       </c>
       <c r="H438" t="n">
         <v>5.8</v>
@@ -13913,7 +13899,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -13932,7 +13918,7 @@
         <v>14.31037507832368</v>
       </c>
       <c r="G439" t="n">
-        <v>12.32873265826606</v>
+        <v>12.32834337418994</v>
       </c>
       <c r="H439" t="n">
         <v>5.9</v>
@@ -13946,7 +13932,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -13963,7 +13949,7 @@
         <v>14.32324581145128</v>
       </c>
       <c r="G440" t="n">
-        <v>12.30743266988259</v>
+        <v>12.30776243229854</v>
       </c>
       <c r="H440" t="n">
         <v>5.4</v>
@@ -13977,7 +13963,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -13994,7 +13980,7 @@
         <v>14.3255836986859</v>
       </c>
       <c r="G441" t="n">
-        <v>12.31075242954278</v>
+        <v>12.31056328295361</v>
       </c>
       <c r="H441" t="n">
         <v>5.1</v>
@@ -14008,7 +13994,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -14027,7 +14013,7 @@
         <v>14.33044751859058</v>
       </c>
       <c r="G442" t="n">
-        <v>12.31304635928397</v>
+        <v>12.3138502377036</v>
       </c>
       <c r="H442" t="n">
         <v>4.7</v>
@@ -14041,7 +14027,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -14058,7 +14044,7 @@
         <v>14.33949739179309</v>
       </c>
       <c r="G443" t="n">
-        <v>12.3179493844158</v>
+        <v>12.31866891983256</v>
       </c>
       <c r="H443" t="n">
         <v>4.5</v>
@@ -14072,7 +14058,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -14089,7 +14075,7 @@
         <v>14.36471173014011</v>
       </c>
       <c r="G444" t="n">
-        <v>12.31955310503318</v>
+        <v>12.32132358925693</v>
       </c>
       <c r="H444" t="n">
         <v>4.1</v>
@@ -14103,7 +14089,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -14122,7 +14108,7 @@
         <v>14.38215927108785</v>
       </c>
       <c r="G445" t="n">
-        <v>12.30474081732688</v>
+        <v>12.30763596093962</v>
       </c>
       <c r="H445" t="n">
         <v>3.9</v>
@@ -14136,7 +14122,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -14153,7 +14139,7 @@
         <v>14.40760072727119</v>
       </c>
       <c r="G446" t="n">
-        <v>12.31720696068138</v>
+        <v>12.32133250064212</v>
       </c>
       <c r="H446" t="n">
         <v>4</v>
@@ -14167,7 +14153,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -14184,7 +14170,7 @@
         <v>14.42640158298136</v>
       </c>
       <c r="G447" t="n">
-        <v>12.3206906778434</v>
+        <v>12.32493509840612</v>
       </c>
       <c r="H447" t="n">
         <v>3.9</v>
@@ -14198,7 +14184,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -14217,7 +14203,7 @@
         <v>14.44539946418754</v>
       </c>
       <c r="G448" t="n">
-        <v>12.32964776353386</v>
+        <v>12.33217211469982</v>
       </c>
       <c r="H448" t="n">
         <v>3.7</v>
@@ -14231,7 +14217,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -14248,7 +14234,7 @@
         <v>14.46426008812566</v>
       </c>
       <c r="G449" t="n">
-        <v>12.34055108955991</v>
+        <v>12.34254221747523</v>
       </c>
       <c r="H449" t="n">
         <v>3.7</v>
@@ -14262,7 +14248,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -14279,7 +14265,7 @@
         <v>14.46989819901403</v>
       </c>
       <c r="G450" t="n">
-        <v>12.33058852022774</v>
+        <v>12.33282423212169</v>
       </c>
       <c r="H450" t="n">
         <v>3.6</v>
@@ -14293,7 +14279,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -14312,7 +14298,7 @@
         <v>14.46797583835696</v>
       </c>
       <c r="G451" t="n">
-        <v>12.32755549509305</v>
+        <v>12.33035893357102</v>
       </c>
       <c r="H451" t="n">
         <v>3.6</v>
@@ -14326,7 +14312,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -14343,7 +14329,7 @@
         <v>14.46984206333199</v>
       </c>
       <c r="G452" t="n">
-        <v>12.31780183804461</v>
+        <v>12.31810584920595</v>
       </c>
       <c r="H452" t="n">
         <v>3.5</v>
@@ -14357,7 +14343,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -14374,7 +14360,7 @@
         <v>14.46682533788225</v>
       </c>
       <c r="G453" t="n">
-        <v>12.32325105399192</v>
+        <v>12.32239683981697</v>
       </c>
       <c r="H453" t="n">
         <v>3.6</v>
@@ -14388,7 +14374,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -14407,7 +14393,7 @@
         <v>14.46673618137315</v>
       </c>
       <c r="G454" t="n">
-        <v>12.31643264292626</v>
+        <v>12.31524986828613</v>
       </c>
       <c r="H454" t="n">
         <v>3.5</v>
@@ -14421,7 +14407,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -14438,7 +14424,7 @@
         <v>14.46489757765088</v>
       </c>
       <c r="G455" t="n">
-        <v>12.32110077881422</v>
+        <v>12.31848573323416</v>
       </c>
       <c r="H455" t="n">
         <v>3.6</v>
@@ -14452,7 +14438,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -14469,7 +14455,7 @@
         <v>14.46759509004912</v>
       </c>
       <c r="G456" t="n">
-        <v>12.30461396321799</v>
+        <v>12.29998184441887</v>
       </c>
       <c r="H456" t="n">
         <v>3.6</v>
@@ -14483,7 +14469,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -14502,7 +14488,7 @@
         <v>14.47141059659744</v>
       </c>
       <c r="G457" t="n">
-        <v>12.2927227072533</v>
+        <v>12.28740375362855</v>
       </c>
       <c r="H457" t="n">
         <v>3.5</v>
@@ -14516,7 +14502,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -14533,7 +14519,7 @@
         <v>14.4872389860009</v>
       </c>
       <c r="G458" t="n">
-        <v>12.33020879071422</v>
+        <v>12.32193383562386</v>
       </c>
       <c r="H458" t="n">
         <v>3.5</v>
@@ -14547,7 +14533,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -14564,7 +14550,7 @@
         <v>14.49414189154477</v>
       </c>
       <c r="G459" t="n">
-        <v>12.31480596687875</v>
+        <v>12.30364390353312</v>
       </c>
       <c r="H459" t="n">
         <v>3.6</v>
@@ -14578,7 +14564,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -14597,7 +14583,7 @@
         <v>14.50887371519958</v>
       </c>
       <c r="G460" t="n">
-        <v>12.30298608488133</v>
+        <v>12.28794751991461</v>
       </c>
       <c r="H460" t="n">
         <v>3.5</v>
@@ -14611,7 +14597,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -14628,7 +14614,7 @@
         <v>14.52301271112058</v>
       </c>
       <c r="G461" t="n">
-        <v>12.3077172657922</v>
+        <v>12.29037243281445</v>
       </c>
       <c r="H461" t="n">
         <v>3.4</v>
@@ -14642,7 +14628,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -14659,7 +14645,7 @@
         <v>14.53525195655051</v>
       </c>
       <c r="G462" t="n">
-        <v>12.31117562802918</v>
+        <v>12.2938133398366</v>
       </c>
       <c r="H462" t="n">
         <v>3.6</v>
@@ -14673,7 +14659,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -14692,7 +14678,7 @@
         <v>14.54510152265352</v>
       </c>
       <c r="G463" t="n">
-        <v>12.3136975954205</v>
+        <v>12.29485245791576</v>
       </c>
       <c r="H463" t="n">
         <v>3.6</v>
@@ -14706,7 +14692,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -14723,7 +14709,7 @@
         <v>14.54961492390578</v>
       </c>
       <c r="G464" t="n">
-        <v>12.31367065612819</v>
+        <v>12.2912590248909</v>
       </c>
       <c r="H464" t="n">
         <v>3.5</v>
@@ -14737,7 +14723,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -14754,7 +14740,7 @@
         <v>14.56146458691081</v>
       </c>
       <c r="G465" t="n">
-        <v>12.31813266928346</v>
+        <v>12.29280981826258</v>
       </c>
       <c r="H465" t="n">
         <v>3.7</v>
@@ -14768,7 +14754,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -14787,7 +14773,7 @@
         <v>14.56559368317529</v>
       </c>
       <c r="G466" t="n">
-        <v>12.32100718362227</v>
+        <v>12.29409268032011</v>
       </c>
       <c r="H466" t="n">
         <v>3.7</v>
@@ -14801,7 +14787,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -14818,7 +14804,7 @@
         <v>14.57612664937282</v>
       </c>
       <c r="G467" t="n">
-        <v>12.31490462866623</v>
+        <v>12.28782312490039</v>
       </c>
       <c r="H467" t="n">
         <v>3.9</v>
@@ -14832,7 +14818,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -14849,7 +14835,7 @@
         <v>14.59038748388755</v>
       </c>
       <c r="G468" t="n">
-        <v>12.31224183412388</v>
+        <v>12.28426441049642</v>
       </c>
       <c r="H468" t="n">
         <v>3.7</v>
@@ -14863,7 +14849,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -14882,7 +14868,7 @@
         <v>14.59246841540046</v>
       </c>
       <c r="G469" t="n">
-        <v>12.31170212501399</v>
+        <v>12.28315867885445</v>
       </c>
       <c r="H469" t="n">
         <v>3.8</v>
@@ -14896,7 +14882,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -14913,7 +14899,7 @@
         <v>14.60015748602528</v>
       </c>
       <c r="G470" t="n">
-        <v>12.30009108230268</v>
+        <v>12.27047834534738</v>
       </c>
       <c r="H470" t="n">
         <v>3.7</v>
@@ -14927,7 +14913,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -14944,7 +14930,7 @@
         <v>14.61343433373368</v>
       </c>
       <c r="G471" t="n">
-        <v>12.30306776865626</v>
+        <v>12.27245477867028</v>
       </c>
       <c r="H471" t="n">
         <v>3.9</v>
@@ -14958,7 +14944,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -14977,7 +14963,7 @@
         <v>14.610362429792</v>
       </c>
       <c r="G472" t="n">
-        <v>12.30208258044877</v>
+        <v>12.26759098550859</v>
       </c>
       <c r="H472" t="n">
         <v>3.9</v>
@@ -14991,7 +14977,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -15008,7 +14994,7 @@
         <v>14.61332806605701</v>
       </c>
       <c r="G473" t="n">
-        <v>12.29985893753434</v>
+        <v>12.26622186024091</v>
       </c>
       <c r="H473" t="n">
         <v>3.9</v>
@@ -15022,7 +15008,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -15039,7 +15025,7 @@
         <v>14.6187871150678</v>
       </c>
       <c r="G474" t="n">
-        <v>12.30686775556507</v>
+        <v>12.26993906585859</v>
       </c>
       <c r="H474" t="n">
         <v>3.9</v>
@@ -15053,7 +15039,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -15072,7 +15058,7 @@
         <v>14.62138043668667</v>
       </c>
       <c r="G475" t="n">
-        <v>12.30681802782444</v>
+        <v>12.26792944907528</v>
       </c>
       <c r="H475" t="n">
         <v>4.1</v>
@@ -15086,7 +15072,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -15103,7 +15089,7 @@
         <v>14.62218327945388</v>
       </c>
       <c r="G476" t="n">
-        <v>12.31432148595917</v>
+        <v>12.2776348800418</v>
       </c>
       <c r="H476" t="n">
         <v>4.2</v>
@@ -15117,7 +15103,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -15134,7 +15120,7 @@
         <v>14.6246516190411</v>
       </c>
       <c r="G477" t="n">
-        <v>12.31017587113</v>
+        <v>12.27160754511783</v>
       </c>
       <c r="H477" t="n">
         <v>4.2</v>
@@ -15148,7 +15134,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -15167,7 +15153,7 @@
         <v>14.63224743838327</v>
       </c>
       <c r="G478" t="n">
-        <v>12.31663858940777</v>
+        <v>12.2774067741345</v>
       </c>
       <c r="H478" t="n">
         <v>4.1</v>
@@ -15181,7 +15167,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -15198,7 +15184,7 @@
         <v>14.63256553503696</v>
       </c>
       <c r="G479" t="n">
-        <v>12.32120327778375</v>
+        <v>12.28309849938073</v>
       </c>
       <c r="H479" t="n">
         <v>4.1</v>
@@ -15212,7 +15198,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -15229,7 +15215,7 @@
         <v>14.63204150520918</v>
       </c>
       <c r="G480" t="n">
-        <v>12.32338445906774</v>
+        <v>12.28596918867604</v>
       </c>
       <c r="H480" t="n">
         <v>4.2</v>
@@ -15243,7 +15229,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -15262,7 +15248,7 @@
         <v>14.63035399641818</v>
       </c>
       <c r="G481" t="n">
-        <v>12.32756435111625</v>
+        <v>12.29141053969487</v>
       </c>
       <c r="H481" t="n">
         <v>4.1</v>
@@ -15276,7 +15262,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -15293,7 +15279,7 @@
         <v>14.6313411919407</v>
       </c>
       <c r="G482" t="n">
-        <v>12.31489565981505</v>
+        <v>12.28027525606269</v>
       </c>
       <c r="H482" t="n">
         <v>4</v>
@@ -15307,7 +15293,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -15324,7 +15310,7 @@
         <v>14.63344331020716</v>
       </c>
       <c r="G483" t="n">
-        <v>12.31308679318466</v>
+        <v>12.27323116896231</v>
       </c>
       <c r="H483" t="n">
         <v>4.2</v>
@@ -15338,7 +15324,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -15357,7 +15343,7 @@
         <v>14.62921913318647</v>
       </c>
       <c r="G484" t="n">
-        <v>12.3291527380874</v>
+        <v>12.28882705782252</v>
       </c>
       <c r="H484" t="n">
         <v>4.2</v>
@@ -15371,7 +15357,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -15388,7 +15374,7 @@
         <v>14.63255935078877</v>
       </c>
       <c r="G485" t="n">
-        <v>12.32629714283654</v>
+        <v>12.28824232037369</v>
       </c>
       <c r="H485" t="n">
         <v>4.2</v>
@@ -15402,7 +15388,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -15419,7 +15405,7 @@
         <v>14.62396036717966</v>
       </c>
       <c r="G486" t="n">
-        <v>12.31427212750686</v>
+        <v>12.27280095483062</v>
       </c>
       <c r="H486" t="n">
         <v>4.3</v>
@@ -15433,7 +15419,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -15452,7 +15438,7 @@
         <v>14.62096760143647</v>
       </c>
       <c r="G487" t="n">
-        <v>12.31866445226598</v>
+        <v>12.27954613072532</v>
       </c>
       <c r="H487" t="n">
         <v>4.1</v>
@@ -15466,7 +15452,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -15483,7 +15469,7 @@
         <v>14.62316117996352</v>
       </c>
       <c r="G488" t="n">
-        <v>12.32792738055661</v>
+        <v>12.28646759885024</v>
       </c>
       <c r="H488" t="n">
         <v>4.3</v>
@@ -15497,7 +15483,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -15514,7 +15500,7 @@
         <v>14.62288958728487</v>
       </c>
       <c r="G489" t="n">
-        <v>12.32746693054715</v>
+        <v>12.28603381141773</v>
       </c>
       <c r="H489" t="n">
         <v>4.3</v>
@@ -15528,7 +15514,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -15547,7 +15533,7 @@
         <v>14.62457191784485</v>
       </c>
       <c r="G490" t="n">
-        <v>12.32746693054715</v>
+        <v>12.28386204718468</v>
       </c>
       <c r="H490" t="n">
         <v>4.4</v>
@@ -15561,7 +15547,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -15586,7 +15572,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -15603,7 +15589,7 @@
         <v>14.61334472741381</v>
       </c>
       <c r="G492" t="n">
-        <v>12.32839204298772</v>
+        <v>12.2877447941742</v>
       </c>
       <c r="H492" t="n">
         <v>4.5</v>
@@ -15617,7 +15603,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -15636,7 +15622,7 @@
         <v>14.61119401978392</v>
       </c>
       <c r="G493" t="n">
-        <v>12.32541890316262</v>
+        <v>12.28592302701791</v>
       </c>
       <c r="H493" t="n">
         <v>4.4</v>
@@ -15650,7 +15636,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -15667,7 +15653,7 @@
         <v>14.60198231195267</v>
       </c>
       <c r="G494" t="n">
-        <v>12.32342003074913</v>
+        <v>12.27796065539001</v>
       </c>
       <c r="H494" t="n">
         <v>4.3</v>
@@ -15681,7 +15667,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -15698,7 +15684,7 @@
         <v>14.59926734245711</v>
       </c>
       <c r="G495" t="n">
-        <v>12.32993494275113</v>
+        <v>12.28394530805027</v>
       </c>
       <c r="H495" t="n">
         <v>4.4</v>
@@ -15712,7 +15698,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -15731,7 +15717,7 @@
         <v>14.60369469918941</v>
       </c>
       <c r="G496" t="n">
-        <v>12.33835450781672</v>
+        <v>12.29177775305455</v>
       </c>
       <c r="H496" t="n">
         <v>4.3</v>
@@ -15745,7 +15731,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -15756,13 +15742,13 @@
         <v>3.908014984030607</v>
       </c>
       <c r="E497" t="n">
-        <v>4.630626409392525</v>
+        <v>4.630611786309793</v>
       </c>
       <c r="F497" t="n">
         <v>14.58942218568114</v>
       </c>
       <c r="G497" t="n">
-        <v>12.33869612612728</v>
+        <v>12.29124984143764</v>
       </c>
       <c r="H497" t="n">
         <v>4.3</v>
@@ -15776,7 +15762,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -15787,13 +15773,13 @@
         <v>3.802208139420939</v>
       </c>
       <c r="E498" t="n">
-        <v>4.631223823183653</v>
+        <v>4.632037992104393</v>
       </c>
       <c r="F498" t="n">
         <v>14.58949828168852</v>
       </c>
       <c r="G498" t="n">
-        <v>12.34327915164455</v>
+        <v>12.29682700879864</v>
       </c>
       <c r="H498" t="n">
         <v>4.3</v>
@@ -15807,7 +15793,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -15820,13 +15806,13 @@
         <v>3.901972669574645</v>
       </c>
       <c r="E499" t="n">
-        <v>4.63319382989431</v>
+        <v>4.634350275750418</v>
       </c>
       <c r="F499" t="n">
         <v>14.59820132343421</v>
       </c>
       <c r="G499" t="n">
-        <v>12.35063608572153</v>
+        <v>12.30308591970017</v>
       </c>
       <c r="H499" t="n">
         <v>4.2</v>
@@ -15840,7 +15826,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -15851,13 +15837,13 @@
         <v>4.01096295328305</v>
       </c>
       <c r="E500" t="n">
-        <v>4.635169667815152</v>
+        <v>4.63667466698405</v>
       </c>
       <c r="F500" t="n">
         <v>14.59688562526572</v>
       </c>
       <c r="G500" t="n">
-        <v>12.34451632807819</v>
+        <v>12.29827345078135</v>
       </c>
       <c r="H500" t="n">
         <v>4.1</v>
@@ -15871,7 +15857,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -15882,13 +15868,13 @@
         <v>3.945457781514384</v>
       </c>
       <c r="E501" t="n">
-        <v>4.635390905036694</v>
+        <v>4.637312057000156</v>
       </c>
       <c r="F501" t="n">
         <v>14.60538918058396</v>
       </c>
       <c r="G501" t="n">
-        <v>12.35289654997097</v>
+        <v>12.30712539607662</v>
       </c>
       <c r="H501" t="n">
         <v>4.1</v>
@@ -15902,7 +15888,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -15910,13 +15896,19 @@
         <v>3.94</v>
       </c>
       <c r="D502" t="inlineStr"/>
-      <c r="E502" t="inlineStr"/>
+      <c r="E502" t="n">
+        <v>4.643915786293136</v>
+      </c>
       <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
+      <c r="G502" t="n">
+        <v>12.30834038347775</v>
+      </c>
       <c r="H502" t="n">
         <v>4.2</v>
       </c>
-      <c r="I502" t="inlineStr"/>
+      <c r="I502" t="n">
+        <v>5.819904872958058</v>
+      </c>
       <c r="J502" t="n">
         <v>4.737600973168581</v>
       </c>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,64 +435,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>GDPlevel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TBILL3M</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ConsSent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CONSspend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CPI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>BrentUSD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>SP500</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -503,7 +517,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -528,7 +542,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="n">
@@ -555,7 +569,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -580,7 +594,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -605,7 +619,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="n">
@@ -632,7 +646,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -657,7 +671,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -682,7 +696,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="n">
@@ -709,7 +723,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -734,7 +748,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -759,7 +773,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="n">
@@ -786,7 +800,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -811,7 +825,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -836,7 +850,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="n">
@@ -863,7 +877,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -888,7 +902,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -913,7 +927,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="n">
@@ -940,7 +954,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -965,7 +979,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -990,7 +1004,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="n">
@@ -1017,7 +1031,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1042,7 +1056,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1067,7 +1081,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="n">
@@ -1094,7 +1108,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1119,7 +1133,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1144,7 +1158,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="n">
@@ -1171,7 +1185,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1196,7 +1210,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1223,7 +1237,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="n">
@@ -1252,7 +1266,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1279,7 +1293,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1306,7 +1320,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="n">
@@ -1335,7 +1349,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1362,7 +1376,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1389,7 +1403,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="n">
@@ -1418,7 +1432,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1445,7 +1459,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1472,7 +1486,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="n">
@@ -1501,7 +1515,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1528,7 +1542,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1555,7 +1569,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="n">
@@ -1584,7 +1598,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1611,7 +1625,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1638,7 +1652,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="n">
@@ -1667,7 +1681,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1694,7 +1708,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1721,7 +1735,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="n">
@@ -1750,7 +1764,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1777,7 +1791,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1804,7 +1818,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="n">
@@ -1833,7 +1847,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1860,7 +1874,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1887,7 +1901,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="n">
@@ -1916,7 +1930,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1943,7 +1957,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1970,7 +1984,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="n">
@@ -1999,7 +2013,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2026,7 +2040,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2053,7 +2067,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="n">
@@ -2082,7 +2096,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2109,7 +2123,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2136,7 +2150,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="n">
@@ -2165,7 +2179,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2192,7 +2206,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2219,7 +2233,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="n">
@@ -2248,7 +2262,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2275,7 +2289,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2302,7 +2316,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="n">
@@ -2331,7 +2345,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2358,7 +2372,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2385,7 +2399,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="n">
@@ -2414,7 +2428,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2441,7 +2455,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2468,7 +2482,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="n">
@@ -2497,7 +2511,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2524,7 +2538,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2551,7 +2565,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="n">
@@ -2580,7 +2594,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2607,7 +2621,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2634,7 +2648,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="n">
@@ -2663,7 +2677,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2690,7 +2704,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2717,7 +2731,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="n">
@@ -2746,7 +2760,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2775,7 +2789,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2804,7 +2818,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="n">
@@ -2835,7 +2849,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2864,7 +2878,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2893,7 +2907,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="n">
@@ -2924,7 +2938,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2953,7 +2967,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2982,7 +2996,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="n">
@@ -3013,7 +3027,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3042,7 +3056,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3071,7 +3085,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="n">
@@ -3102,7 +3116,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3133,7 +3147,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3164,7 +3178,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="n">
@@ -3197,7 +3211,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3228,7 +3242,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3259,7 +3273,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="n">
@@ -3292,7 +3306,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -3323,7 +3337,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -3354,7 +3368,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="n">
@@ -3387,7 +3401,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -3418,7 +3432,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3449,7 +3463,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="n">
@@ -3482,7 +3496,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -3513,7 +3527,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3544,7 +3558,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="n">
@@ -3577,7 +3591,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -3608,7 +3622,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3639,7 +3653,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="n">
@@ -3672,7 +3686,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -3703,7 +3717,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3734,7 +3748,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="n">
@@ -3767,7 +3781,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3798,7 +3812,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3829,7 +3843,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="n">
@@ -3862,7 +3876,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -3893,7 +3907,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -3924,7 +3938,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -3957,7 +3971,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -3988,7 +4002,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4019,7 +4033,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -4052,7 +4066,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4083,7 +4097,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4114,7 +4128,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -4147,7 +4161,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4178,7 +4192,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4209,7 +4223,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -4242,7 +4256,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -4273,7 +4287,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4304,7 +4318,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -4337,7 +4351,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -4368,7 +4382,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4399,7 +4413,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -4432,7 +4446,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -4463,7 +4477,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -4494,7 +4508,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -4527,7 +4541,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -4558,7 +4572,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -4589,7 +4603,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -4622,7 +4636,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -4653,7 +4667,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4684,7 +4698,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -4717,7 +4731,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -4748,7 +4762,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4779,7 +4793,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -4812,7 +4826,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -4843,7 +4857,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -4874,7 +4888,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -4907,7 +4921,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -4938,7 +4952,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -4969,7 +4983,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -5002,7 +5016,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -5033,7 +5047,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5064,7 +5078,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -5097,7 +5111,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5128,7 +5142,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5159,7 +5173,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -5192,7 +5206,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -5223,7 +5237,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5254,7 +5268,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -5287,7 +5301,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -5318,7 +5332,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -5349,7 +5363,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -5382,7 +5396,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -5413,7 +5427,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -5444,7 +5458,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -5477,7 +5491,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5508,7 +5522,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5539,7 +5553,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -5572,7 +5586,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -5603,7 +5617,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -5634,7 +5648,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -5667,7 +5681,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -5698,7 +5712,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -5729,7 +5743,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -5762,7 +5776,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -5793,7 +5807,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -5824,7 +5838,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -5857,7 +5871,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -5888,7 +5902,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -5919,7 +5933,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -5952,7 +5966,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -5983,7 +5997,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -6014,7 +6028,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -6047,7 +6061,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -6078,7 +6092,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -6109,7 +6123,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -6142,7 +6156,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -6173,7 +6187,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -6204,7 +6218,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -6237,7 +6251,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -6268,7 +6282,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -6299,7 +6313,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -6332,7 +6346,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -6363,7 +6377,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -6394,7 +6408,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -6427,7 +6441,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -6458,7 +6472,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -6489,7 +6503,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -6522,7 +6536,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -6553,7 +6567,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -6584,7 +6598,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -6617,7 +6631,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -6648,7 +6662,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -6679,7 +6693,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -6712,7 +6726,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -6743,7 +6757,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -6774,7 +6788,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -6807,7 +6821,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -6838,7 +6852,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -6869,7 +6883,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -6902,7 +6916,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -6933,7 +6947,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -6964,7 +6978,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -6997,7 +7011,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -7028,7 +7042,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -7059,7 +7073,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -7092,7 +7106,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -7123,7 +7137,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -7154,7 +7168,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -7187,7 +7201,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -7218,7 +7232,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -7249,7 +7263,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -7282,7 +7296,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -7313,7 +7327,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -7344,7 +7358,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -7377,7 +7391,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -7408,7 +7422,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -7439,7 +7453,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -7472,7 +7486,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -7503,7 +7517,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -7534,7 +7548,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -7567,7 +7581,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -7598,7 +7612,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -7629,7 +7643,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -7662,7 +7676,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -7693,7 +7707,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -7724,7 +7738,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -7757,7 +7771,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -7788,7 +7802,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -7819,7 +7833,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -7852,7 +7866,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -7883,7 +7897,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -7914,7 +7928,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -7947,7 +7961,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7978,7 +7992,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -8009,7 +8023,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -8042,7 +8056,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -8073,7 +8087,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -8104,7 +8118,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -8137,7 +8151,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -8168,7 +8182,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -8199,7 +8213,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -8232,7 +8246,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -8263,7 +8277,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -8294,7 +8308,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -8327,7 +8341,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -8358,7 +8372,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -8389,7 +8403,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -8422,7 +8436,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -8453,7 +8467,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -8484,7 +8498,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -8517,7 +8531,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -8548,7 +8562,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -8579,7 +8593,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -8612,7 +8626,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -8643,7 +8657,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -8674,7 +8688,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -8707,7 +8721,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -8738,7 +8752,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -8769,7 +8783,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -8802,7 +8816,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -8833,7 +8847,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -8864,7 +8878,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -8897,7 +8911,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -8928,7 +8942,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -8959,7 +8973,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -8992,7 +9006,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -9023,7 +9037,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -9054,7 +9068,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -9087,7 +9101,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -9118,7 +9132,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -9149,7 +9163,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -9182,7 +9196,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -9213,7 +9227,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -9244,7 +9258,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -9277,7 +9291,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -9308,7 +9322,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -9339,7 +9353,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -9372,7 +9386,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -9403,7 +9417,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -9434,7 +9448,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -9467,7 +9481,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -9498,7 +9512,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -9529,7 +9543,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -9562,7 +9576,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -9593,7 +9607,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -9624,7 +9638,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -9657,7 +9671,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -9688,7 +9702,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -9719,7 +9733,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -9752,7 +9766,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -9783,7 +9797,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -9814,7 +9828,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -9847,7 +9861,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -9878,7 +9892,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -9909,7 +9923,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -9942,7 +9956,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -9973,7 +9987,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -10004,7 +10018,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -10037,7 +10051,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -10068,7 +10082,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -10099,7 +10113,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -10132,7 +10146,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -10163,7 +10177,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -10194,7 +10208,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -10227,7 +10241,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -10258,7 +10272,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -10289,7 +10303,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -10322,7 +10336,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -10353,7 +10367,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -10384,7 +10398,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -10417,7 +10431,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -10448,7 +10462,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -10479,7 +10493,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -10512,7 +10526,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -10543,7 +10557,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -10574,7 +10588,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -10607,7 +10621,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -10638,7 +10652,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -10669,7 +10683,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -10702,7 +10716,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -10733,7 +10747,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -10764,7 +10778,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -10797,7 +10811,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -10828,7 +10842,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -10859,7 +10873,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -10892,7 +10906,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -10923,7 +10937,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -10954,7 +10968,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -10987,7 +11001,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -11018,7 +11032,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -11049,7 +11063,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -11082,7 +11096,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -11113,7 +11127,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -11144,7 +11158,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -11177,7 +11191,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -11208,7 +11222,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -11239,7 +11253,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -11272,7 +11286,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -11303,7 +11317,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -11334,7 +11348,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -11367,7 +11381,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -11398,7 +11412,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -11429,7 +11443,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -11462,7 +11476,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -11493,7 +11507,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -11524,7 +11538,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -11557,7 +11571,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -11588,7 +11602,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -11619,7 +11633,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -11652,7 +11666,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -11683,7 +11697,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -11714,7 +11728,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -11747,7 +11761,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -11778,7 +11792,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -11809,7 +11823,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -11842,7 +11856,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -11873,7 +11887,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -11904,7 +11918,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -11937,7 +11951,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -11968,7 +11982,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -11999,7 +12013,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -12032,7 +12046,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -12063,7 +12077,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -12094,7 +12108,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -12127,7 +12141,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -12158,7 +12172,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -12189,7 +12203,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -12222,7 +12236,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -12253,7 +12267,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -12284,7 +12298,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -12317,7 +12331,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -12348,7 +12362,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -12379,7 +12393,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -12412,7 +12426,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -12443,7 +12457,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -12474,7 +12488,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -12507,7 +12521,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -12538,7 +12552,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -12569,7 +12583,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -12602,7 +12616,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -12633,7 +12647,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -12664,7 +12678,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -12697,7 +12711,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -12728,7 +12742,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -12759,7 +12773,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -12792,7 +12806,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -12823,7 +12837,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -12854,7 +12868,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -12887,7 +12901,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -12918,7 +12932,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -12949,7 +12963,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -12982,7 +12996,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -13013,7 +13027,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -13044,7 +13058,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -13077,7 +13091,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -13108,7 +13122,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -13139,7 +13153,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -13172,7 +13186,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -13203,7 +13217,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -13234,7 +13248,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -13267,7 +13281,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -13298,7 +13312,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -13329,7 +13343,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -13362,7 +13376,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -13393,7 +13407,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -13424,7 +13438,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -13457,7 +13471,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -13488,7 +13502,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -13519,7 +13533,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -13552,7 +13566,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -13583,7 +13597,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -13614,7 +13628,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -13647,7 +13661,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -13678,7 +13692,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -13709,7 +13723,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -13742,7 +13756,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -13773,7 +13787,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -13804,7 +13818,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -13837,7 +13851,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -13868,7 +13882,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -13899,7 +13913,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -13932,7 +13946,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -13963,7 +13977,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -13994,7 +14008,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -14027,7 +14041,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -14058,7 +14072,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -14089,7 +14103,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -14122,7 +14136,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -14153,7 +14167,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -14184,7 +14198,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -14217,7 +14231,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -14248,7 +14262,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -14279,7 +14293,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -14312,7 +14326,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -14343,7 +14357,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -14374,7 +14388,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -14407,7 +14421,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -14438,7 +14452,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -14469,7 +14483,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -14502,7 +14516,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -14533,7 +14547,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -14564,7 +14578,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -14597,7 +14611,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -14628,7 +14642,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -14659,7 +14673,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -14692,7 +14706,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -14723,7 +14737,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -14754,7 +14768,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -14787,7 +14801,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -14818,7 +14832,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -14849,7 +14863,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -14882,7 +14896,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -14913,7 +14927,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -14944,7 +14958,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -14977,7 +14991,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -15008,7 +15022,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -15039,7 +15053,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -15072,7 +15086,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -15103,7 +15117,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -15134,7 +15148,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -15167,7 +15181,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -15198,7 +15212,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -15229,7 +15243,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -15262,7 +15276,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -15293,7 +15307,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -15324,7 +15338,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -15357,7 +15371,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -15388,7 +15402,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -15419,7 +15433,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -15452,7 +15466,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -15483,7 +15497,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -15514,7 +15528,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -15547,7 +15561,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -15572,7 +15586,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -15603,7 +15617,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -15636,7 +15650,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -15667,7 +15681,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -15698,7 +15712,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -15731,7 +15745,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -15762,7 +15776,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -15793,7 +15807,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -15826,7 +15840,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -15857,7 +15871,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -15888,14 +15902,16 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
       <c r="C502" t="n">
         <v>3.94</v>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="n">
+        <v>3.873282177111716</v>
+      </c>
       <c r="E502" t="n">
         <v>4.643915786293136</v>
       </c>

--- a/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/US_data_inspect_noreal_sent_levels_auth.xlsx
@@ -15905,7 +15905,9 @@
       <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="n">
+        <v>10.11095190512563</v>
+      </c>
       <c r="C502" t="n">
         <v>3.94</v>
       </c>
